--- a/output/sliding_window_results_window_10.xlsx
+++ b/output/sliding_window_results_window_10.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>34.4</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
-        <v>34.00997604643288</v>
+        <v>57.02767011333387</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3900239535671162</v>
+        <v>4.027670113333869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.152118684356124</v>
+        <v>16.22212654184286</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>36.3</v>
+        <v>56.1</v>
       </c>
       <c r="C3" t="n">
-        <v>35.39962308963304</v>
+        <v>61.03792524974904</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9003769103669583</v>
+        <v>4.937925249749036</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8106785807219498</v>
+        <v>24.38310577210908</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C4" t="n">
-        <v>37.19631729236753</v>
+        <v>61.33006223534556</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.303682707632468</v>
+        <v>1.330062235345558</v>
       </c>
       <c r="E4" t="n">
-        <v>1.699588602179924</v>
+        <v>1.769065549892423</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C5" t="n">
-        <v>38.8932285178963</v>
+        <v>71.55343875472801</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.206771482103697</v>
+        <v>7.653438754728008</v>
       </c>
       <c r="E5" t="n">
-        <v>1.456297410018754</v>
+        <v>58.5751247723726</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>40.28037132978429</v>
+        <v>76.5892630531699</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.219628670215712</v>
+        <v>5.989263053169907</v>
       </c>
       <c r="E6" t="n">
-        <v>1.487494093212147</v>
+        <v>35.87127192006611</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>43.71630625573654</v>
+        <v>81.32375288031</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01630625573653788</v>
+        <v>0.4237528803099906</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002658939761453744</v>
+        <v>0.1795665035710132</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>45.61320644715109</v>
+        <v>89.62426534507711</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.486793552848908</v>
+        <v>0.5242653450771115</v>
       </c>
       <c r="E8" t="n">
-        <v>6.184142174490897</v>
+        <v>0.2748541520488229</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C9" t="n">
-        <v>50.25088637875854</v>
+        <v>85.96460286741669</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.749113621241456</v>
+        <v>-9.035397132583313</v>
       </c>
       <c r="E9" t="n">
-        <v>7.557625702495312</v>
+        <v>81.63840134349475</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C10" t="n">
-        <v>54.44302340517366</v>
+        <v>100.7772246127182</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.65697659482634</v>
+        <v>1.977224612718189</v>
       </c>
       <c r="E10" t="n">
-        <v>2.745571435802291</v>
+        <v>3.909417169138591</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C11" t="n">
-        <v>58.07785508478483</v>
+        <v>99.46988185147208</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.922144915215171</v>
+        <v>-3.830118148527916</v>
       </c>
       <c r="E11" t="n">
-        <v>3.694641075087536</v>
+        <v>14.66980503168291</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C12" t="n">
-        <v>61.39279105826952</v>
+        <v>109.9235690390623</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.507208941730475</v>
+        <v>2.923569039062329</v>
       </c>
       <c r="E12" t="n">
-        <v>6.28609667749325</v>
+        <v>8.54725592616383</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>70.59999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="C13" t="n">
-        <v>68.93729019297123</v>
+        <v>117.9904348877884</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.662709807028762</v>
+        <v>9.290434887788408</v>
       </c>
       <c r="E13" t="n">
-        <v>2.764603902389621</v>
+        <v>86.312180404236</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>80.90000000000001</v>
+        <v>112.7</v>
       </c>
       <c r="C14" t="n">
-        <v>76.98461726039352</v>
+        <v>119.3857036584123</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.915382739606486</v>
+        <v>6.685703658412251</v>
       </c>
       <c r="E14" t="n">
-        <v>15.33022199760839</v>
+        <v>44.69863340810696</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>89.09999999999999</v>
+        <v>117.2</v>
       </c>
       <c r="C15" t="n">
-        <v>85.18032154974469</v>
+        <v>125.660591057253</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.919678450255304</v>
+        <v>8.460591057252984</v>
       </c>
       <c r="E15" t="n">
-        <v>15.36387915339582</v>
+        <v>71.58160103806917</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>95</v>
+        <v>123.1</v>
       </c>
       <c r="C16" t="n">
-        <v>90.9417510758694</v>
+        <v>126.9340355089138</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.058248924130595</v>
+        <v>3.834035508913757</v>
       </c>
       <c r="E16" t="n">
-        <v>16.46938433020713</v>
+        <v>14.69982828361158</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>98.8</v>
+        <v>128.9</v>
       </c>
       <c r="C17" t="n">
-        <v>95.21781594160694</v>
+        <v>129.7498825795373</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.582184058393054</v>
+        <v>0.8498825795373364</v>
       </c>
       <c r="E17" t="n">
-        <v>12.83204262820533</v>
+        <v>0.7223003990010369</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>103.3</v>
+        <v>135.1</v>
       </c>
       <c r="C18" t="n">
-        <v>99.79443719539168</v>
+        <v>136.1197153474624</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.505562804608317</v>
+        <v>1.01971534746238</v>
       </c>
       <c r="E18" t="n">
-        <v>12.28897057705333</v>
+        <v>1.039819389850323</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>107</v>
+        <v>139.4</v>
       </c>
       <c r="C19" t="n">
-        <v>103.7665795684162</v>
+        <v>140.4607726974175</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.233420431583795</v>
+        <v>1.060772697417462</v>
       </c>
       <c r="E19" t="n">
-        <v>10.45500768738354</v>
+        <v>1.125238715586319</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>108.7</v>
+        <v>143.8</v>
       </c>
       <c r="C20" t="n">
-        <v>105.8526725708435</v>
+        <v>149.0174101197005</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.84732742915655</v>
+        <v>5.217410119700475</v>
       </c>
       <c r="E20" t="n">
-        <v>8.10727348882725</v>
+        <v>27.22136835715292</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>112.7</v>
+        <v>147.2</v>
       </c>
       <c r="C21" t="n">
-        <v>110.0171747461303</v>
+        <v>153.387463000576</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.682825253869751</v>
+        <v>6.187463000576031</v>
       </c>
       <c r="E21" t="n">
-        <v>7.197551342801296</v>
+        <v>38.28469838349734</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-45.73375499264438</v>
+        <v>59.52766485944385</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>132.883455437706</v>
+        <v>531.7256630614946</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>6.644172771885302</v>
+        <v>26.58628315307473</v>
       </c>
     </row>
   </sheetData>
